--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487995_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487995_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.8326</v>
+        <v>5.1485</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8076</v>
+        <v>2.4043</v>
       </c>
       <c r="F2" t="n">
-        <v>3.025</v>
+        <v>2.7442</v>
       </c>
       <c r="G2" t="n">
         <v>1.9206</v>
@@ -610,13 +610,13 @@
         <v>3.3698</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4449</v>
+        <v>0.7608</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2322</v>
+        <v>0.8289</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2127</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.2867</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VERKERK</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3089</v>
+        <v>1.9594</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3514</v>
+        <v>-0.5234</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9575</v>
+        <v>2.4828</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>1.6478</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1034</v>
+        <v>1.2727</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3966</v>
+        <v>0.3751</v>
       </c>
       <c r="J3" t="n">
-        <v>2.6088</v>
+        <v>1.8128</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3594</v>
+        <v>1.9981</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2494</v>
+        <v>-0.1853</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.1087</v>
+        <v>-0.165</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.256</v>
+        <v>-0.7255</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1472</v>
+        <v>0.5604</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1893</v>
+        <v>0.1982</v>
       </c>
       <c r="Q3" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R3" t="n">
-        <v>1.784</v>
+        <v>3.1716</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1944</v>
+        <v>0.2341</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1125</v>
+        <v>0.1039</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0819</v>
+        <v>0.1301</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.1962</v>
+        <v>-0.1207</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6036</v>
+        <v>0.5331</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.7997</v>
+        <v>-0.6539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>J. VERKERK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0007</v>
+        <v>1.8992</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2013</v>
+        <v>0.5594</v>
       </c>
       <c r="F4" t="n">
-        <v>2.202</v>
+        <v>1.3398</v>
       </c>
       <c r="G4" t="n">
-        <v>1.6478</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
-        <v>1.2727</v>
+        <v>1.1034</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3751</v>
+        <v>1.3966</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8128</v>
+        <v>2.6088</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9981</v>
+        <v>1.3594</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1853</v>
+        <v>1.2494</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.165</v>
+        <v>-0.1087</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7255</v>
+        <v>-0.256</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5604</v>
+        <v>0.1472</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1982</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.9733</v>
       </c>
       <c r="R4" t="n">
-        <v>3.1716</v>
+        <v>1.784</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2754</v>
+        <v>0.7846</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4261</v>
+        <v>0.3204</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1506</v>
+        <v>0.4642</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1207</v>
+        <v>-0.1962</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5331</v>
+        <v>0.6036</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6539</v>
+        <v>-0.7997</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0326</v>
+        <v>1.5763</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7784</v>
+        <v>-0.2066</v>
       </c>
       <c r="F5" t="n">
-        <v>1.811</v>
+        <v>1.7829</v>
       </c>
       <c r="G5" t="n">
         <v>-0.6178</v>
@@ -844,13 +844,13 @@
         <v>2.1805</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.885</v>
+        <v>-0.3414</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4881</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3969</v>
+        <v>-0.425</v>
       </c>
       <c r="V5" t="n">
         <v>0.5532</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1129</v>
+        <v>0.3334</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2515</v>
+        <v>-0.0872</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3644</v>
+        <v>0.4205</v>
       </c>
       <c r="G8" t="n">
         <v>0.0645</v>
@@ -1078,13 +1078,13 @@
         <v>0.5947</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5462</v>
+        <v>-0.3258</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.312</v>
+        <v>-0.1477</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2342</v>
+        <v>-0.1781</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. RAGA RODRIGUEZ</t>
+          <t>P. RODRIGUEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8296</v>
+        <v>-0.4636</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3711</v>
+        <v>-1.0913</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4584</v>
+        <v>0.6277</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7718</v>
+        <v>-1.624</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1958</v>
+        <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.576</v>
+        <v>-1.7352</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6798999999999999</v>
+        <v>-1.0611</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2787</v>
+        <v>0.9685</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5988</v>
+        <v>-2.0296</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4517</v>
+        <v>-0.5629</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4745</v>
+        <v>-0.8574000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.0228</v>
+        <v>0.2945</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5947</v>
+        <v>1.9822</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1805</v>
+        <v>-1.1893</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7751</v>
+        <v>3.1716</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2085</v>
+        <v>-0.7010999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8629</v>
+        <v>-0.3146</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3456</v>
+        <v>-0.3865</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.861</v>
+        <v>-0.1207</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2666</v>
+        <v>1.4737</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1275</v>
+        <v>-1.5944</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ SANCHEZ</t>
+          <t>R. RAGA RODRIGUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1987</v>
+        <v>-1.6425</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4615</v>
+        <v>-0.9594</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2627</v>
+        <v>-0.6831</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.624</v>
+        <v>-0.7718</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1112</v>
+        <v>-0.1958</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.7352</v>
+        <v>-0.576</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0611</v>
+        <v>0.6798999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9685</v>
+        <v>1.2787</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0296</v>
+        <v>-0.5988</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5629</v>
+        <v>-1.4517</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8574000000000001</v>
+        <v>-1.4745</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2945</v>
+        <v>0.0228</v>
       </c>
       <c r="P10" t="n">
-        <v>1.9822</v>
+        <v>0.5947</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1893</v>
+        <v>-2.1805</v>
       </c>
       <c r="R10" t="n">
-        <v>3.1716</v>
+        <v>2.7751</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.4363</v>
+        <v>0.3956</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.6847</v>
+        <v>0.2746</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7516</v>
+        <v>0.121</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1207</v>
+        <v>-1.861</v>
       </c>
       <c r="W10" t="n">
-        <v>1.4737</v>
+        <v>0.2666</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.5944</v>
+        <v>-2.1275</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7894</v>
+        <v>-2.4941</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9112</v>
+        <v>-2.7283</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1219</v>
+        <v>0.2342</v>
       </c>
       <c r="G11" t="n">
         <v>-2.1359</v>
@@ -1312,13 +1312,13 @@
         <v>2.5769</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.041</v>
+        <v>0.2542</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1635</v>
+        <v>0.0195</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1225</v>
+        <v>0.2348</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2071</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3929</v>
+        <v>-3.8606</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.9407</v>
+        <v>-4.4084</v>
       </c>
       <c r="F12" t="n">
         <v>0.5479000000000001</v>
@@ -1390,10 +1390,10 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5947</v>
+        <v>-0.0624</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.4037</v>
       </c>
       <c r="U12" t="n">
         <v>0.3413</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3883</v>
+        <v>-5.519</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7918</v>
+        <v>-5.2595</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5965</v>
+        <v>-0.2595</v>
       </c>
       <c r="G13" t="n">
         <v>-5.6247</v>
@@ -1468,13 +1468,13 @@
         <v>1.9822</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0233</v>
+        <v>-0.1541</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0387</v>
+        <v>-0.5064</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0154</v>
+        <v>0.3523</v>
       </c>
       <c r="V13" t="n">
         <v>-0.5331</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-3.1058</v>
+        <v>-1.857599999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.3431</v>
+        <v>-11.095</v>
       </c>
       <c r="F14" t="n">
-        <v>9.237500000000001</v>
+        <v>9.237400000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-6.4918</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.4456</v>
+        <v>-2.445600000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-4.0463</v>
@@ -1534,7 +1534,7 @@
         <v>-8.652200000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8502999999999998</v>
+        <v>0.8503000000000001</v>
       </c>
       <c r="P14" t="n">
         <v>7.928999999999999</v>
@@ -1546,13 +1546,13 @@
         <v>22.7957</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4033</v>
+        <v>0.8444999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9892999999999997</v>
+        <v>0.2585000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5861</v>
+        <v>0.5860000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-4.1394</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. PALOMARES CALDERON</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1753</v>
+        <v>3.0276</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4022</v>
+        <v>1.9134</v>
       </c>
       <c r="F15" t="n">
-        <v>4.773</v>
+        <v>1.1142</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2715</v>
+        <v>1.2597</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6575</v>
+        <v>-0.2614</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6141</v>
+        <v>1.5211</v>
       </c>
       <c r="J15" t="n">
-        <v>1.6091</v>
+        <v>2.0921</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2403</v>
+        <v>0.9956</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6312</v>
+        <v>1.0965</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3376</v>
+        <v>-0.8324</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5828</v>
+        <v>-1.257</v>
       </c>
       <c r="O15" t="n">
-        <v>1.2452</v>
+        <v>0.4246</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.9733</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q15" t="n">
-        <v>-5.9467</v>
+        <v>-1.9822</v>
       </c>
       <c r="R15" t="n">
-        <v>2.9733</v>
+        <v>1.5858</v>
       </c>
       <c r="S15" t="n">
-        <v>4.9297</v>
+        <v>-0.446</v>
       </c>
       <c r="T15" t="n">
-        <v>2.5259</v>
+        <v>-0.1329</v>
       </c>
       <c r="U15" t="n">
-        <v>2.4038</v>
+        <v>-0.3131</v>
       </c>
       <c r="V15" t="n">
-        <v>2.9474</v>
+        <v>2.6104</v>
       </c>
       <c r="W15" t="n">
-        <v>3.2139</v>
+        <v>1.9364</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2666</v>
+        <v>0.674</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>C. PALOMARES CALDERON</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4871</v>
+        <v>2.9716</v>
       </c>
       <c r="E16" t="n">
-        <v>0.5368000000000001</v>
+        <v>-0.5333</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9503</v>
+        <v>3.5049</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7733</v>
+        <v>1.2715</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9532</v>
+        <v>0.6575</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1799</v>
+        <v>0.6141</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4706</v>
+        <v>1.6091</v>
       </c>
       <c r="K16" t="n">
-        <v>1.0694</v>
+        <v>2.2403</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5988</v>
+        <v>-0.6312</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3027</v>
+        <v>-0.3376</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.1162</v>
+        <v>-1.5828</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4189</v>
+        <v>1.2452</v>
       </c>
       <c r="P16" t="n">
-        <v>1.784</v>
+        <v>-2.9733</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-5.9467</v>
       </c>
       <c r="R16" t="n">
-        <v>1.784</v>
+        <v>2.9733</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1963</v>
+        <v>1.7261</v>
       </c>
       <c r="T16" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.5904</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1301</v>
+        <v>1.1357</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2666</v>
+        <v>2.9474</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.2139</v>
       </c>
       <c r="X16" t="n">
         <v>-0.2666</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.367</v>
+        <v>2.4395</v>
       </c>
       <c r="E17" t="n">
-        <v>1.921</v>
+        <v>1.7173</v>
       </c>
       <c r="F17" t="n">
-        <v>0.446</v>
+        <v>0.7222</v>
       </c>
       <c r="G17" t="n">
         <v>2.2138</v>
@@ -1780,13 +1780,13 @@
         <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2918</v>
+        <v>-0.2193</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2568</v>
+        <v>-0.4606</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.035</v>
+        <v>0.2412</v>
       </c>
       <c r="V17" t="n">
         <v>-0.7444</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6099</v>
+        <v>2.3127</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9966</v>
+        <v>0.2312</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6133999999999999</v>
+        <v>2.0815</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2597</v>
+        <v>0.7733</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2614</v>
+        <v>0.9532</v>
       </c>
       <c r="I18" t="n">
-        <v>1.5211</v>
+        <v>-0.1799</v>
       </c>
       <c r="J18" t="n">
-        <v>2.0921</v>
+        <v>0.4706</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9956</v>
+        <v>1.0694</v>
       </c>
       <c r="L18" t="n">
-        <v>1.0965</v>
+        <v>-0.5988</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8324</v>
+        <v>0.3027</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.257</v>
+        <v>-0.1162</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4246</v>
+        <v>0.4189</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3964</v>
+        <v>1.784</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>1.784</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8637</v>
+        <v>0.022</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0497</v>
+        <v>-0.2394</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8139999999999999</v>
+        <v>0.2614</v>
       </c>
       <c r="V18" t="n">
-        <v>2.6104</v>
+        <v>-0.2666</v>
       </c>
       <c r="W18" t="n">
-        <v>1.9364</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.674</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0715</v>
+        <v>-0.6686</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9579</v>
+        <v>-1.5504</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8863</v>
+        <v>0.8818</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0564</v>
@@ -1936,13 +1936,13 @@
         <v>0.7929</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8169</v>
+        <v>-0.4139</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8112</v>
+        <v>-0.4037</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0057</v>
+        <v>-0.0103</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6863</v>
+        <v>-1.2273</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5031</v>
+        <v>-3.0956</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8167</v>
+        <v>1.8683</v>
       </c>
       <c r="G20" t="n">
         <v>0.2089</v>
@@ -2014,13 +2014,13 @@
         <v>0.7929</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2985</v>
+        <v>0.1606</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4881</v>
+        <v>-0.08069999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1896</v>
+        <v>0.2412</v>
       </c>
       <c r="V20" t="n">
         <v>-0.4074</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>W. EL OTMANI MOHAMED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.2586</v>
+        <v>-1.5368</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8644</v>
+        <v>-2.4576</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6057</v>
+        <v>0.9208</v>
       </c>
       <c r="G21" t="n">
-        <v>2.1227</v>
+        <v>0.0582</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.08309999999999999</v>
+        <v>2.3253</v>
       </c>
       <c r="I21" t="n">
-        <v>2.2059</v>
+        <v>-2.2671</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2742</v>
+        <v>0.6928</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4986</v>
+        <v>3.2486</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7756</v>
+        <v>-2.5558</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1515</v>
+        <v>-0.6346000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5818</v>
+        <v>-0.9233</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4303</v>
+        <v>0.2888</v>
       </c>
       <c r="P21" t="n">
-        <v>-5.7485</v>
+        <v>-1.3876</v>
       </c>
       <c r="Q21" t="n">
-        <v>-7.9289</v>
+        <v>-2.9733</v>
       </c>
       <c r="R21" t="n">
-        <v>2.1805</v>
+        <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1005</v>
+        <v>-0.2074</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0501</v>
+        <v>-0.177</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0505</v>
+        <v>-0.0304</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7403</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.4737</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.3089</v>
+        <v>-1.891</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5605</v>
+        <v>-2.2549</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2515</v>
+        <v>0.3638</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3757</v>
@@ -2170,13 +2170,13 @@
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.3459</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.312</v>
+        <v>-0.0064</v>
       </c>
       <c r="U22" t="n">
-        <v>0.24</v>
+        <v>0.3523</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2666</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>W. EL OTMANI MOHAMED</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.6593</v>
+        <v>-2.5094</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9669</v>
+        <v>-3.4756</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3076</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0582</v>
+        <v>2.1227</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3253</v>
+        <v>-0.08309999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.2671</v>
+        <v>2.2059</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6928</v>
+        <v>2.2742</v>
       </c>
       <c r="K23" t="n">
-        <v>3.2486</v>
+        <v>0.4986</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.5558</v>
+        <v>1.7756</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.1515</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9233</v>
+        <v>-0.5818</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2888</v>
+        <v>0.4303</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.3876</v>
+        <v>-5.7485</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9733</v>
+        <v>-7.9289</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5858</v>
+        <v>2.1805</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.33</v>
+        <v>0.8498</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6864</v>
+        <v>0.4388</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6435999999999999</v>
+        <v>0.4109</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.7403</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.4737</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.654700000000001</v>
+        <v>2.9183</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.996199999999998</v>
+        <v>-9.5055</v>
       </c>
       <c r="F24" t="n">
-        <v>11.6505</v>
+        <v>12.4237</v>
       </c>
       <c r="G24" t="n">
         <v>6.476</v>
@@ -2296,13 +2296,13 @@
         <v>3.0152</v>
       </c>
       <c r="I24" t="n">
-        <v>3.461099999999999</v>
+        <v>3.4611</v>
       </c>
       <c r="J24" t="n">
         <v>7.4191</v>
       </c>
       <c r="K24" t="n">
-        <v>8.430100000000001</v>
+        <v>8.430099999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-1.0109</v>
@@ -2317,7 +2317,7 @@
         <v>4.472</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.514700000000001</v>
+        <v>-9.514699999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-22.7955</v>
@@ -2326,13 +2326,13 @@
         <v>13.2809</v>
       </c>
       <c r="S24" t="n">
-        <v>1.5536</v>
+        <v>1.8178</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0379999999999997</v>
+        <v>-0.4714999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.5157</v>
+        <v>2.2889</v>
       </c>
       <c r="V24" t="n">
         <v>4.1394</v>
